--- a/reports/Week-to-Week-Comparison/07-06-2026 - Week to Week Comparison.xlsx
+++ b/reports/Week-to-Week-Comparison/07-06-2026 - Week to Week Comparison.xlsx
@@ -628,7 +628,7 @@
         <v>404</v>
       </c>
       <c r="C3" s="5">
-        <v>0</v>
+        <v>371</v>
       </c>
       <c r="D3" s="5">
         <v>323</v>
@@ -678,7 +678,7 @@
         <v>42</v>
       </c>
       <c r="C4" s="5">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D4" s="5">
         <v>37</v>
@@ -728,7 +728,7 @@
         <v>362</v>
       </c>
       <c r="C5" s="5">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="D5" s="5">
         <v>286</v>
@@ -778,7 +778,7 @@
         <v>38</v>
       </c>
       <c r="C6" s="7">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D6" s="7">
         <v>17</v>
@@ -975,49 +975,49 @@
         <v>16</v>
       </c>
       <c r="B12" s="3">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="C12" s="3">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="D12" s="3">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="E12" s="3">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="F12" s="3">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="G12" s="3">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="H12" s="3">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="I12" s="3">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="J12" s="3">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="K12" s="3">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="L12" s="3">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="M12" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="N12" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O12" s="3">
         <v>0</v>
       </c>
       <c r="P12" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="16" customHeight="1">
@@ -1275,37 +1275,37 @@
         <v>22</v>
       </c>
       <c r="B18" s="10">
-        <v>0.116504854368932</v>
+        <v>0.2330097087378641</v>
       </c>
       <c r="C18" s="10">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0.2682926829268293</v>
+      </c>
+      <c r="E18" s="10">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="F18" s="10">
         <v>0.1111111111111111</v>
       </c>
-      <c r="D18" s="10">
-        <v>0.1341463414634146</v>
-      </c>
-      <c r="E18" s="10">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="F18" s="10">
-        <v>0.05555555555555555</v>
-      </c>
       <c r="G18" s="10">
-        <v>0.04545454545454546</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="H18" s="10">
-        <v>0.07894736842105263</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="I18" s="10">
-        <v>0.03125</v>
+        <v>0.0625</v>
       </c>
       <c r="J18" s="10">
-        <v>0.06578947368421052</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="K18" s="10">
-        <v>0.02380952380952381</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="L18" s="10">
-        <v>0.01298701298701299</v>
+        <v>0.02597402597402598</v>
       </c>
       <c r="M18" s="10">
         <v>0</v>
